--- a/SistemaDinamicoDados/AmostrasFiltradas/KrigingVsg-2d/content/KrigingMetrics.xlsx
+++ b/SistemaDinamicoDados/AmostrasFiltradas/KrigingVsg-2d/content/KrigingMetrics.xlsx
@@ -477,28 +477,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-119.0737550397648</v>
+        <v>-1896.024204093585</v>
       </c>
       <c r="B2" t="n">
-        <v>15.30263957410662</v>
+        <v>456.8023264259097</v>
       </c>
       <c r="C2" t="n">
-        <v>91.0578778769988</v>
+        <v>440.8602591064754</v>
       </c>
       <c r="D2" t="n">
-        <v>3.911858838724452</v>
+        <v>21.37293443647619</v>
       </c>
       <c r="E2" t="n">
-        <v>-32718059595.46437</v>
+        <v>-73427.23325849489</v>
       </c>
       <c r="F2" t="n">
-        <v>994425045.2932043</v>
+        <v>12090.67341919551</v>
       </c>
       <c r="G2" t="n">
-        <v>35215.57565402731</v>
+        <v>353.5946876659316</v>
       </c>
       <c r="H2" t="n">
-        <v>31534.50562944034</v>
+        <v>109.9575982785888</v>
       </c>
     </row>
   </sheetData>
@@ -562,25 +562,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.697420043240527e-26</v>
+        <v>4.791905474772092e-25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.746046099831028e-12</v>
+        <v>3.308503033906332e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>1.642382429046453e-13</v>
+        <v>6.922359044987548e-13</v>
       </c>
       <c r="E2" t="n">
-        <v>-13.79325709895614</v>
+        <v>0.96032349071072</v>
       </c>
       <c r="F2" t="n">
-        <v>0.108268907555035</v>
+        <v>0.006533123499534328</v>
       </c>
       <c r="G2" t="n">
-        <v>1.46828889325411</v>
+        <v>0.108944959986798</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3290424099641793</v>
+        <v>0.08082773966612161</v>
       </c>
     </row>
   </sheetData>
@@ -644,25 +644,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7.346155511086911e-26</v>
+        <v>1.279850956576173e-24</v>
       </c>
       <c r="C2" t="n">
-        <v>1.548252909480955e-12</v>
+        <v>4.206833897288238e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>2.710379219055317e-13</v>
+        <v>1.13130497947113e-12</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.57551294617975</v>
+        <v>0.9799460673825205</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03097443501578886</v>
+        <v>0.003302075227588925</v>
       </c>
       <c r="G2" t="n">
-        <v>8.765109139048382</v>
+        <v>0.08419849960716481</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1759955539659706</v>
+        <v>0.05746368616429792</v>
       </c>
     </row>
   </sheetData>
@@ -726,25 +726,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.441205468848537e-27</v>
+        <v>4.206374340171254e-25</v>
       </c>
       <c r="C2" t="n">
-        <v>2.531634804693874e-13</v>
+        <v>2.83048252879981e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>4.940855663595666e-14</v>
+        <v>6.485656744055496e-13</v>
       </c>
       <c r="E2" t="n">
-        <v>-15.63470089084013</v>
+        <v>0.8586620574650461</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007059367898800818</v>
+        <v>0.02327266814271948</v>
       </c>
       <c r="G2" t="n">
-        <v>1.543407400158848</v>
+        <v>0.1735363863321548</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08402004462508228</v>
+        <v>0.1525538204789361</v>
       </c>
     </row>
   </sheetData>
@@ -805,28 +805,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0.9999999996119735</v>
       </c>
       <c r="B2" t="n">
-        <v>2.411118935361594e-29</v>
+        <v>9.343655770505802e-11</v>
       </c>
       <c r="C2" t="n">
-        <v>2.446065816331317e-14</v>
+        <v>0.0002291119959665836</v>
       </c>
       <c r="D2" t="n">
-        <v>4.910314588049928e-15</v>
+        <v>9.666258723262998e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.292812858962954</v>
+        <v>0.9999250836640439</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00084743836115934</v>
+        <v>1.233570401482558e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2655097992744396</v>
+        <v>0.06064400080190788</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02911079458138063</v>
+        <v>0.003512222090760432</v>
       </c>
     </row>
   </sheetData>
@@ -890,25 +890,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.345808219934205e-30</v>
+        <v>2.212829410471568e-24</v>
       </c>
       <c r="C2" t="n">
-        <v>1.05126731853092e-14</v>
+        <v>6.88537570467651e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>2.084660216902075e-15</v>
+        <v>1.4875582040618e-12</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.909989903919418</v>
+        <v>0.9960691934375552</v>
       </c>
       <c r="F2" t="n">
-        <v>7.160661953412217e-05</v>
+        <v>0.0006472455663374157</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06187588705667843</v>
+        <v>0.06407074142915291</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008462069459306167</v>
+        <v>0.02544102133046973</v>
       </c>
     </row>
   </sheetData>
